--- a/list.xlsx
+++ b/list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\flutter\welfare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C4F84F-8573-4805-A2BD-73AA1E21ACE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4EA4F4-83A2-4253-B557-F2349A7C56A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>url</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,29 +39,55 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>encoding</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>utf-8</t>
-  </si>
-  <si>
-    <t>新北</t>
-  </si>
-  <si>
     <t>https://www.sw.ntpc.gov.tw/home.jsp?id=5afc03e40d8c7154</t>
   </si>
   <si>
     <t>./NewTaipei/main1.py</t>
   </si>
   <si>
-    <t>桃園</t>
-  </si>
-  <si>
     <t>https://sab.tycg.gov.tw/cl.aspx?n=7313</t>
   </si>
   <si>
     <t>./Taoyuan/main1.py</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.klcg.gov.tw/tw/social/2748.html</t>
+  </si>
+  <si>
+    <t>./Keelung/main1.py</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基隆市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘉義市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://social.chiayi.gov.tw/cl.aspx?n=379</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>志願服務暫未處理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>./ChiayiCity/main1.py</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -69,7 +95,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,6 +155,13 @@
       <color theme="1"/>
       <name val="MingLiU"/>
       <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
       <charset val="136"/>
     </font>
   </fonts>
@@ -168,7 +201,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
@@ -190,6 +223,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -487,45 +529,57 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="41.65" thickBot="1">
+      <c r="A2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="105.4" thickBot="1">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="105.4" thickBot="1">
-      <c r="A2" s="4" t="s">
+      <c r="C3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" ht="60.4" thickBot="1">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="60.4" thickBot="1">
-      <c r="A3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4" ht="75.400000000000006" thickBot="1">
+      <c r="A5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" ht="15.4" thickBot="1">
-      <c r="A4" s="3"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.4" thickBot="1">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4" ht="15.4" thickBot="1">
@@ -561,9 +615,11 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{6B24962D-C1B8-44B0-9509-4295523AA2BD}"/>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{6B24962D-C1B8-44B0-9509-4295523AA2BD}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{2CFE921E-39E8-420C-A759-CFEE5B1AFF02}"/>
+    <hyperlink ref="B2" r:id="rId3" xr:uid="{CB2A7D7F-A475-42D9-B230-0E62850979FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/list.xlsx
+++ b/list.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\flutter\welfare\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\welfare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4EA4F4-83A2-4253-B557-F2349A7C56A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B242372-DC4A-47CB-939B-DCD742075148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>url</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -88,6 +88,56 @@
   </si>
   <si>
     <t>./ChiayiCity/main1.py</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://welfare.yunlin.gov.tw/Home/WelfareList/63?Type=A</t>
+  </si>
+  <si>
+    <t>./Yunlin/main1.py</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雲林縣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新竹市</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>page</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>請留空</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://society.hccg.gov.tw/ch/home.jsp?id=73&amp;parentpath=0,2,12&amp;mcustomize=&amp;serno=null&amp;page=</t>
+  </si>
+  <si>
+    <t>./HsinchuCity/main1.py</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新竹縣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://social.hsinchu.gov.tw/cl.aspx?n=202</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>./Hsinchu/main1.py</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -95,7 +145,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,6 +211,20 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
     </font>
@@ -201,7 +265,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
@@ -234,6 +298,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -515,10 +586,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1">
+    <row r="1" spans="1:4" ht="17.25" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -532,94 +603,122 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="41.65" thickBot="1">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:4" ht="45" thickBot="1">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" ht="45.75" thickBot="1">
+      <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D3" s="11" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="105.4" thickBot="1">
-      <c r="A3" s="4" t="s">
+    <row r="4" spans="1:4" ht="111" thickBot="1">
+      <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" ht="60.4" thickBot="1">
-      <c r="A4" s="8" t="s">
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4" ht="63.75" thickBot="1">
+      <c r="A5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" ht="75.400000000000006" thickBot="1">
-      <c r="A5" s="10" t="s">
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" ht="79.5" thickBot="1">
+      <c r="A6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" ht="15.4" thickBot="1">
-      <c r="A6" s="3"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
       <c r="D6" s="3"/>
     </row>
-    <row r="7" spans="1:4" ht="15.4" thickBot="1">
-      <c r="A7" s="3"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
+    <row r="7" spans="1:4" ht="111" thickBot="1">
+      <c r="A7" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>18</v>
+      </c>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" ht="15.4" thickBot="1">
-      <c r="A8" s="5"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.4" thickBot="1">
+    <row r="8" spans="1:4" ht="174" thickBot="1">
+      <c r="A8" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="16.5" thickBot="1">
       <c r="A9" s="5"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" ht="15.4" thickBot="1">
+    <row r="10" spans="1:4" ht="16.5" thickBot="1">
       <c r="A10" s="5"/>
       <c r="B10" s="2"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
+    <row r="11" spans="1:4" ht="16.5" thickBot="1">
+      <c r="A11" s="5"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{6B24962D-C1B8-44B0-9509-4295523AA2BD}"/>
-    <hyperlink ref="B5" r:id="rId2" xr:uid="{2CFE921E-39E8-420C-A759-CFEE5B1AFF02}"/>
-    <hyperlink ref="B2" r:id="rId3" xr:uid="{CB2A7D7F-A475-42D9-B230-0E62850979FE}"/>
+    <hyperlink ref="B4" r:id="rId1" xr:uid="{6B24962D-C1B8-44B0-9509-4295523AA2BD}"/>
+    <hyperlink ref="B6" r:id="rId2" xr:uid="{2CFE921E-39E8-420C-A759-CFEE5B1AFF02}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{CB2A7D7F-A475-42D9-B230-0E62850979FE}"/>
+    <hyperlink ref="B7" r:id="rId4" display="https://welfare.yunlin.gov.tw/" xr:uid="{5E87293A-17A4-40FA-BDAE-68FE0FAD6DC5}"/>
+    <hyperlink ref="B2" r:id="rId5" xr:uid="{D522E3A6-626A-41FC-9429-7700F816DAF0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/list.xlsx
+++ b/list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\welfare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B242372-DC4A-47CB-939B-DCD742075148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43EAB55-0811-4483-BDB3-FA9A29C542C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -715,8 +715,8 @@
     <hyperlink ref="B4" r:id="rId1" xr:uid="{6B24962D-C1B8-44B0-9509-4295523AA2BD}"/>
     <hyperlink ref="B6" r:id="rId2" xr:uid="{2CFE921E-39E8-420C-A759-CFEE5B1AFF02}"/>
     <hyperlink ref="B3" r:id="rId3" xr:uid="{CB2A7D7F-A475-42D9-B230-0E62850979FE}"/>
-    <hyperlink ref="B7" r:id="rId4" display="https://welfare.yunlin.gov.tw/" xr:uid="{5E87293A-17A4-40FA-BDAE-68FE0FAD6DC5}"/>
-    <hyperlink ref="B2" r:id="rId5" xr:uid="{D522E3A6-626A-41FC-9429-7700F816DAF0}"/>
+    <hyperlink ref="B2" r:id="rId4" xr:uid="{D522E3A6-626A-41FC-9429-7700F816DAF0}"/>
+    <hyperlink ref="B7" r:id="rId5" display="https://welfare.yunlin.gov.tw/" xr:uid="{5E87293A-17A4-40FA-BDAE-68FE0FAD6DC5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>

--- a/list.xlsx
+++ b/list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\welfare\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43EAB55-0811-4483-BDB3-FA9A29C542C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F05747-B6D1-4665-BA51-6AB9433CB834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="180" yWindow="3870" windowWidth="16410" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>url</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -45,99 +45,11 @@
     <t>./NewTaipei/main1.py</t>
   </si>
   <si>
-    <t>https://sab.tycg.gov.tw/cl.aspx?n=7313</t>
-  </si>
-  <si>
-    <t>./Taoyuan/main1.py</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>新北市</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>桃園市</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://www.klcg.gov.tw/tw/social/2748.html</t>
-  </si>
-  <si>
-    <t>./Keelung/main1.py</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基隆市</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>備註</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>嘉義市</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://social.chiayi.gov.tw/cl.aspx?n=379</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>志願服務暫未處理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>./ChiayiCity/main1.py</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://welfare.yunlin.gov.tw/Home/WelfareList/63?Type=A</t>
-  </si>
-  <si>
-    <t>./Yunlin/main1.py</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雲林縣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新竹市</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>page</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>請留空</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://society.hccg.gov.tw/ch/home.jsp?id=73&amp;parentpath=0,2,12&amp;mcustomize=&amp;serno=null&amp;page=</t>
-  </si>
-  <si>
-    <t>./HsinchuCity/main1.py</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>新竹縣</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://social.hsinchu.gov.tw/cl.aspx?n=202</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>./Hsinchu/main1.py</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -145,7 +57,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,46 +97,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Microsoft JhengHei"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="MingLiU"/>
-      <family val="3"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
     </font>
@@ -265,7 +137,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
@@ -277,34 +149,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -586,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1" spans="1:4" ht="17.25" thickBot="1">
@@ -600,125 +444,27 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="45" thickBot="1">
-      <c r="A2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>25</v>
+    <row r="2" spans="1:4" ht="111.75" thickBot="1">
+      <c r="A2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" ht="45.75" thickBot="1">
-      <c r="A3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="111" thickBot="1">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" ht="63.75" thickBot="1">
-      <c r="A5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" ht="79.5" thickBot="1">
-      <c r="A6" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="111" thickBot="1">
-      <c r="A7" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="174" thickBot="1">
-      <c r="A8" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A9" s="5"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A10" s="5"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" ht="16.5" thickBot="1">
-      <c r="A11" s="5"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" xr:uid="{6B24962D-C1B8-44B0-9509-4295523AA2BD}"/>
-    <hyperlink ref="B6" r:id="rId2" xr:uid="{2CFE921E-39E8-420C-A759-CFEE5B1AFF02}"/>
-    <hyperlink ref="B3" r:id="rId3" xr:uid="{CB2A7D7F-A475-42D9-B230-0E62850979FE}"/>
-    <hyperlink ref="B2" r:id="rId4" xr:uid="{D522E3A6-626A-41FC-9429-7700F816DAF0}"/>
-    <hyperlink ref="B7" r:id="rId5" display="https://welfare.yunlin.gov.tw/" xr:uid="{5E87293A-17A4-40FA-BDAE-68FE0FAD6DC5}"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{6B24962D-C1B8-44B0-9509-4295523AA2BD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>